--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-02-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_26-02-2026.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>£15.98</t>
+          <t>£15.94</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='www.insulationshop.co', port=443): Max retries exceeded with url: /80mm_celotex_ga4000_pir_insulation.html (Caused by ConnectTimeoutError(&lt;urllib3.connection.HTTPSConnection object at 0x0000015CF3451110&gt;, 'Connection to www.insulationshop.co timed out. (connect timeout=30)'))</t>
+          <t>£25.89</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1396,7 +1396,30 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>£34.88</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
+  (Session info: chrome=145.0.7632.117); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6dd2daa55
+	0x7ff6dd038630
+	0x7ff6dcdcd75d
+	0x7ff6dce2862e
+	0x7ff6dce2893c
+	0x7ff6dce78d87
+	0x7ff6dce7591c
+	0x7ff6dce19098
+	0x7ff6dce19f83
+	0x7ff6dd307810
+	0x7ff6dd301afd
+	0x7ff6dd322c1a
+	0x7ff6dd053345
+	0x7ff6dd05b81c
+	0x7ff6dd041924
+	0x7ff6dd041ad6
+	0x7ff6dd027e47
+	0x7ff8cb4ae8d7
+	0x7ff8cc6cc40c
+</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1513,7 +1536,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>£32.99</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1615,7 +1638,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>£32.99</t>
+          <t>£32.75</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1707,7 +1730,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>£39.35</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1799,7 +1822,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>£40.01</t>
+          <t>£39.56</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1891,7 +1914,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>£40.36</t>
+          <t>£39.81</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2413,7 +2436,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>£61.03</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2873,7 +2896,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>£1163.76</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out. (read timeout=30)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2995,7 +3018,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£1377.12</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3077,7 +3100,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>£1359.84</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
